--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -5,17 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\12,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDE00FC-26C3-4FE9-841C-C7FD2E0C00EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6C5E68-F1B0-4B6C-8736-00E81AA00A9D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$G$20</definedName>
+  </definedNames>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
   <si>
     <t>Бердянск</t>
   </si>
@@ -96,9 +99,6 @@
     <t>Мариуполь</t>
   </si>
   <si>
-    <t>Мароиуполь ЗПФ</t>
-  </si>
-  <si>
     <t>в третью машину Крыма</t>
   </si>
   <si>
@@ -121,6 +121,12 @@
   </si>
   <si>
     <t>Малахутин</t>
+  </si>
+  <si>
+    <t>ПРС ЛП ЗПФ</t>
+  </si>
+  <si>
+    <t>Мариуполь ЗПФ</t>
   </si>
 </sst>
 </file>
@@ -574,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" customWidth="1"/>
@@ -593,16 +599,16 @@
         <v>6</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>7</v>
@@ -610,7 +616,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="8">
         <v>6652</v>
@@ -643,42 +649,39 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2">
-        <f t="shared" ref="G3:G15" si="0">B3-C3-D3-E3-F3</f>
+        <f t="shared" ref="G3:G16" si="0">B3-C3-D3-E3-F3</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="6">
-        <v>2894</v>
-      </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6">
-        <v>2894</v>
-      </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>15</v>
+      <c r="A4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1528</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2">
+        <v>1528</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B5" s="6">
-        <v>101</v>
+        <v>2894</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6">
-        <v>101</v>
+        <v>2894</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6">
@@ -690,77 +693,80 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="10">
-        <v>1363</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10">
-        <v>1363</v>
-      </c>
-      <c r="G6" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>22</v>
+      <c r="A6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6">
+        <v>101</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
+        <v>101</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B7" s="10">
-        <v>81</v>
+        <v>1363</v>
       </c>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10">
+        <v>1363</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="10">
         <v>81</v>
       </c>
-      <c r="G7" s="10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="2">
-        <v>7211</v>
-      </c>
-      <c r="C8" s="2">
-        <v>3656</v>
-      </c>
-      <c r="D8" s="2">
-        <v>3555</v>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10">
+        <v>81</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>52</v>
-      </c>
-      <c r="C9" s="2"/>
+        <v>7211</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3656</v>
+      </c>
       <c r="D9" s="2">
-        <v>52</v>
+        <v>3555</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -771,14 +777,14 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2">
-        <v>3689</v>
+        <v>52</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2">
-        <v>3689</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -786,20 +792,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B11" s="2">
-        <v>649</v>
+        <v>3689</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2">
-        <v>649</v>
+        <v>3689</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -807,38 +810,38 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="8">
-        <v>5578</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8">
-        <v>5578</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>16</v>
+      <c r="A12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="2">
+        <v>649</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2">
+        <v>649</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B13" s="8">
-        <v>331</v>
+        <v>5578</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8">
-        <v>331</v>
+        <v>5578</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="8"/>
@@ -851,32 +854,35 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="2">
-        <v>2816</v>
-      </c>
-      <c r="C14" s="2">
-        <v>2816</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8">
+        <v>331</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8">
+        <v>331</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2">
-        <v>1084</v>
+        <v>2816</v>
       </c>
       <c r="C15" s="2">
-        <v>1084</v>
+        <v>2816</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -886,69 +892,88 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1084</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1084</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="4">
-        <f>SUM(B2:B15)</f>
-        <v>34780</v>
-      </c>
-      <c r="C16" s="4">
-        <f>SUM(C2:C15)</f>
+      <c r="B17" s="4">
+        <f>SUM(B2:B16)</f>
+        <v>36308</v>
+      </c>
+      <c r="C17" s="4">
+        <f>SUM(C2:C16)</f>
         <v>9835</v>
       </c>
-      <c r="D16" s="4">
-        <f>SUM(D2:D15)</f>
-        <v>20506</v>
-      </c>
-      <c r="E16" s="4">
-        <f>SUM(E2:E15)</f>
+      <c r="D17" s="4">
+        <f>SUM(D2:D16)</f>
+        <v>22034</v>
+      </c>
+      <c r="E17" s="4">
+        <f>SUM(E2:E16)</f>
         <v>2995</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4">
-        <f>SUM(G2:G15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" t="s">
+      <c r="F17" s="4"/>
+      <c r="G17" s="4">
+        <f>SUM(G2:G16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
         <v>17</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D18" t="s">
         <v>18</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="3:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="14" t="s">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C19" s="3">
-        <f>IF(ROUNDUP(C16/500,0)&gt;32,32,ROUNDUP(C16/500,0))</f>
+      <c r="D19" s="15"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="12"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="C20" s="3">
+        <f>IF(ROUNDUP(C17/500,0)&gt;32,32,ROUNDUP(C17/500,0))</f>
         <v>20</v>
       </c>
-      <c r="D19" s="3">
-        <f t="shared" ref="D19:E19" si="1">IF(ROUNDUP(D16/500,0)&gt;32,32,ROUNDUP(D16/500,0))</f>
+      <c r="D20" s="3">
+        <f t="shared" ref="D20:E20" si="1">IF(ROUNDUP(D17/500,0)&gt;32,32,ROUNDUP(D17/500,0))</f>
         <v>32</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E20" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="F19" s="13"/>
+      <c r="F20" s="13"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G20" xr:uid="{48F57757-815D-4339-B327-3C53318A928F}"/>
   <mergeCells count="1">
-    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
